--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.58576710215879</v>
+        <v>4.320187154100804</v>
       </c>
       <c r="D2" t="n">
-        <v>26.60466884565917</v>
+        <v>4.323258687419615</v>
       </c>
       <c r="E2" t="n">
-        <v>10.21977303501321</v>
+        <v>1.660713118189647</v>
       </c>
       <c r="F2" t="n">
-        <v>6.487260680387116</v>
+        <v>1.054179860562906</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.78439756152285</v>
+        <v>6.952464603747464</v>
       </c>
       <c r="D3" t="n">
-        <v>27.34278072454123</v>
+        <v>4.44320186773795</v>
       </c>
       <c r="E3" t="n">
-        <v>10.21977303501321</v>
+        <v>1.660713118189647</v>
       </c>
       <c r="F3" t="n">
-        <v>6.487260680387116</v>
+        <v>1.054179860562906</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.08140055343587</v>
+        <v>5.863227589933329</v>
       </c>
       <c r="D4" t="n">
-        <v>31.73046016361546</v>
+        <v>5.156199776587512</v>
       </c>
       <c r="E4" t="n">
-        <v>10.21977303501321</v>
+        <v>1.660713118189647</v>
       </c>
       <c r="F4" t="n">
-        <v>6.487260680387116</v>
+        <v>1.054179860562906</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.20218536665887</v>
+        <v>2.145355122082067</v>
       </c>
       <c r="D5" t="n">
-        <v>13.17833461458457</v>
+        <v>2.141479374869993</v>
       </c>
       <c r="E5" t="n">
-        <v>10.21977303501321</v>
+        <v>1.660713118189647</v>
       </c>
       <c r="F5" t="n">
-        <v>6.487260680387116</v>
+        <v>1.054179860562906</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.62415120111035</v>
+        <v>5.788924570180432</v>
       </c>
       <c r="D6" t="n">
-        <v>20.01893731372229</v>
+        <v>3.253077313479873</v>
       </c>
       <c r="E6" t="n">
-        <v>10.21977303501321</v>
+        <v>1.660713118189647</v>
       </c>
       <c r="F6" t="n">
-        <v>6.487260680387116</v>
+        <v>1.054179860562906</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
